--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484233_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484233_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.9113</v>
+        <v>8.8879</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9356</v>
+        <v>6.9667</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9757</v>
+        <v>1.9212</v>
       </c>
       <c r="G2" t="n">
         <v>5.333</v>
@@ -610,13 +610,13 @@
         <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0968</v>
+        <v>0.8798</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1086</v>
+        <v>-0.0775</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0118</v>
+        <v>0.9573</v>
       </c>
       <c r="V2" t="n">
         <v>1.8938</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4459</v>
+        <v>3.9008</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4819</v>
+        <v>5.1747</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.036</v>
+        <v>-1.2739</v>
       </c>
       <c r="G3" t="n">
-        <v>4.5519</v>
+        <v>-0.0435</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8143</v>
+        <v>-0.4211</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7377</v>
+        <v>0.3776</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2369</v>
+        <v>1.9581</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1732</v>
+        <v>1.8495</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0638</v>
+        <v>0.1086</v>
       </c>
       <c r="M3" t="n">
-        <v>0.315</v>
+        <v>-2.0016</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3589</v>
+        <v>-2.2707</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.269</v>
       </c>
       <c r="P3" t="n">
         <v>1.1721</v>
@@ -688,28 +688,28 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7027</v>
+        <v>-0.2304</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4404</v>
+        <v>-0.7984</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2623</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.9808</v>
+        <v>3.0027</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>4.2104</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.9808</v>
+        <v>-1.2077</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1986</v>
+        <v>2.812</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6086</v>
+        <v>3.8753</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.4101</v>
+        <v>-1.0633</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0435</v>
+        <v>4.5519</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4211</v>
+        <v>1.8143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3776</v>
+        <v>2.7377</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9581</v>
+        <v>4.2369</v>
       </c>
       <c r="K4" t="n">
-        <v>1.8495</v>
+        <v>2.1732</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1086</v>
+        <v>2.0638</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0016</v>
+        <v>0.315</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2707</v>
+        <v>-0.3589</v>
       </c>
       <c r="O4" t="n">
-        <v>0.269</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P4" t="n">
         <v>1.1721</v>
@@ -766,22 +766,22 @@
         <v>1.3674</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9327</v>
+        <v>0.0688</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3645</v>
+        <v>-0.1663</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4318</v>
+        <v>0.2351</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0027</v>
+        <v>-2.9808</v>
       </c>
       <c r="W4" t="n">
-        <v>4.2104</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2077</v>
+        <v>-2.9808</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5402</v>
+        <v>0.9529</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.026</v>
+        <v>-1.5316</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5662</v>
+        <v>2.4845</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0424</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>1.3872</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8448</v>
+        <v>0.3392</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5424</v>
+        <v>0.4607</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6646</v>
+        <v>0.3711</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2953</v>
+        <v>0.3558</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3693</v>
+        <v>0.0153</v>
       </c>
       <c r="G6" t="n">
         <v>0.4441</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5608</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.226</v>
+        <v>-0.128</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9869</v>
+        <v>-0.8253</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.319</v>
+        <v>-1.1573</v>
       </c>
       <c r="F7" t="n">
         <v>0.3321</v>
@@ -1000,10 +1000,10 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3907</v>
+        <v>-0.229</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4237</v>
+        <v>-0.262</v>
       </c>
       <c r="U7" t="n">
         <v>0.033</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9905</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="E8" t="n">
         <v>-0.1202</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8703</v>
+        <v>-0.8431</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7528</v>
@@ -1078,13 +1078,13 @@
         <v>0.1953</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4331</v>
+        <v>-0.4058</v>
       </c>
       <c r="T8" t="n">
         <v>-0.1816</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.4042</v>
+        <v>-2.1991</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7366</v>
+        <v>0.5696</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.1408</v>
+        <v>-2.7687</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3877</v>
+        <v>-1.5013</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7427</v>
+        <v>-0.0049</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6451</v>
+        <v>-1.4964</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0244</v>
+        <v>0.0716</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3236</v>
+        <v>0.7585</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.7007</v>
+        <v>-0.6869</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3634</v>
+        <v>-1.5729</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.419</v>
+        <v>-0.7634</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9443</v>
+        <v>-0.8095</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>1.3307</v>
+        <v>-0.4436</v>
       </c>
       <c r="T9" t="n">
-        <v>1.761</v>
+        <v>-0.3885</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4303</v>
+        <v>-0.0551</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.7145</v>
+        <v>-1.817</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7145</v>
+        <v>-2.7035</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9831</v>
+        <v>-3.1578</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0035</v>
+        <v>-0.3306</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9866</v>
+        <v>-2.8272</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5013</v>
+        <v>-0.6207</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0049</v>
+        <v>0.0133</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4964</v>
+        <v>-0.634</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0716</v>
+        <v>0.3283</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7585</v>
+        <v>0.2878</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6869</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.5729</v>
+        <v>-0.949</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7634</v>
+        <v>-0.2745</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8095</v>
+        <v>-0.6745</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5627</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2276</v>
+        <v>0.0722</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9546</v>
+        <v>0.0406</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.273</v>
+        <v>0.0316</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.817</v>
+        <v>-1.8279</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.7035</v>
+        <v>-2.1052</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2378</v>
+        <v>-3.2925</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4923</v>
+        <v>-0.3151</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7455</v>
+        <v>-2.9774</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6207</v>
+        <v>-2.3877</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0133</v>
+        <v>-0.7427</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.634</v>
+        <v>-1.6451</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3283</v>
+        <v>-1.0244</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2878</v>
+        <v>-0.3236</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0405</v>
+        <v>-0.7007</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.949</v>
+        <v>-1.3634</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2745</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6745</v>
+        <v>-0.9443</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0077</v>
+        <v>0.4423</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.121</v>
+        <v>0.7093</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1133</v>
+        <v>-0.2669</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8279</v>
+        <v>-2.7145</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1052</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5067</v>
+        <v>-5.8912</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3576</v>
+        <v>-1.7422</v>
       </c>
       <c r="F12" t="n">
         <v>-4.149</v>
@@ -1390,10 +1390,10 @@
         <v>0.586</v>
       </c>
       <c r="S12" t="n">
-        <v>0.864</v>
+        <v>0.4795</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5752</v>
+        <v>0.1906</v>
       </c>
       <c r="U12" t="n">
         <v>0.2888</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.0428</v>
+        <v>-6.3817</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.0454</v>
+        <v>-4.4387</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.9974</v>
+        <v>-1.943</v>
       </c>
       <c r="G13" t="n">
         <v>-3.9085</v>
@@ -1468,13 +1468,13 @@
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7313</v>
+        <v>-0.0701</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1829</v>
+        <v>-0.5762</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4516</v>
+        <v>0.5061</v>
       </c>
       <c r="V13" t="n">
         <v>-1.817</v>
@@ -1501,31 +1501,31 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.391400000000003</v>
+        <v>-5.786100000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>6.701000000000001</v>
+        <v>7.306400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0924</v>
+        <v>-13.0925</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.367400000000002</v>
+        <v>-3.367400000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-8.0892</v>
       </c>
       <c r="I14" t="n">
-        <v>4.721700000000001</v>
+        <v>4.721699999999998</v>
       </c>
       <c r="J14" t="n">
         <v>9.0382</v>
       </c>
       <c r="K14" t="n">
-        <v>2.289299999999999</v>
+        <v>2.2893</v>
       </c>
       <c r="L14" t="n">
-        <v>6.749100000000002</v>
+        <v>6.749099999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-12.4058</v>
@@ -1546,13 +1546,13 @@
         <v>12.6971</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.09610000000000007</v>
+        <v>0.5093000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.5023</v>
+        <v>-1.8971</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4062</v>
+        <v>2.4064</v>
       </c>
       <c r="V14" t="n">
         <v>-7.811400000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.085100000000001</v>
+        <v>7.0594</v>
       </c>
       <c r="E15" t="n">
-        <v>6.8642</v>
+        <v>6.3586</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2209</v>
+        <v>0.7007</v>
       </c>
       <c r="G15" t="n">
         <v>4.4891</v>
@@ -1624,13 +1624,13 @@
         <v>1.1721</v>
       </c>
       <c r="S15" t="n">
-        <v>2.01</v>
+        <v>0.9842</v>
       </c>
       <c r="T15" t="n">
-        <v>0.091</v>
+        <v>-0.4146</v>
       </c>
       <c r="U15" t="n">
-        <v>1.919</v>
+        <v>1.3988</v>
       </c>
       <c r="V15" t="n">
         <v>0.6093</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.0281</v>
+        <v>6.95</v>
       </c>
       <c r="E16" t="n">
         <v>9.133599999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.1056</v>
+        <v>-2.1836</v>
       </c>
       <c r="G16" t="n">
         <v>4.465</v>
@@ -1702,13 +1702,13 @@
         <v>1.1721</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.358</v>
+        <v>-0.4361</v>
       </c>
       <c r="T16" t="n">
         <v>-0.6435999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7144</v>
+        <v>0.2075</v>
       </c>
       <c r="V16" t="n">
         <v>4.8745</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.128</v>
+        <v>5.8372</v>
       </c>
       <c r="E17" t="n">
-        <v>4.7612</v>
+        <v>5.0646</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3668</v>
+        <v>0.7726</v>
       </c>
       <c r="G17" t="n">
         <v>-0.1255</v>
@@ -1780,13 +1780,13 @@
         <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6714</v>
+        <v>0.0378</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4842</v>
+        <v>-0.1808</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1872</v>
+        <v>0.2186</v>
       </c>
       <c r="V17" t="n">
         <v>6.3155</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6158</v>
+        <v>0.983</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1945</v>
+        <v>1.3475</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4213</v>
+        <v>-0.3645</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2611</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.089</v>
+        <v>-0.3034</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3502</v>
+        <v>-0.2294</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4109</v>
+        <v>0.0814</v>
       </c>
       <c r="K18" t="n">
-        <v>0.33</v>
+        <v>0.0409</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1498</v>
+        <v>-0.6142</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.419</v>
+        <v>-0.3443</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2692</v>
+        <v>-0.2698</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5733</v>
+        <v>0.379</v>
       </c>
       <c r="T18" t="n">
-        <v>0.311</v>
+        <v>0.2428</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2623</v>
+        <v>0.1362</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6093</v>
+        <v>0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
         <v>-0.2772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5979</v>
+        <v>0.3836</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0442</v>
+        <v>-0.0078</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4462</v>
+        <v>0.3914</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5328000000000001</v>
+        <v>0.2611</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3034</v>
+        <v>-0.089</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2294</v>
+        <v>0.3502</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0814</v>
+        <v>0.4109</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0409</v>
+        <v>0.33</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6142</v>
+        <v>-0.1498</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3443</v>
+        <v>-0.419</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2698</v>
+        <v>0.2692</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0061</v>
+        <v>0.3411</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0605</v>
+        <v>0.1087</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0545</v>
+        <v>0.2324</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9414</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2186</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6248</v>
+        <v>-0.4535</v>
       </c>
       <c r="E20" t="n">
-        <v>0.07829999999999999</v>
+        <v>-0.0228</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7030999999999999</v>
+        <v>-0.4307</v>
       </c>
       <c r="G20" t="n">
         <v>-2.6737</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2283</v>
+        <v>-0.0571</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4015</v>
+        <v>-0.5026</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1732</v>
+        <v>0.4456</v>
       </c>
       <c r="V20" t="n">
         <v>1.4959</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1336</v>
+        <v>-0.8497</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.2408</v>
+        <v>-0.0386</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8928</v>
+        <v>-0.8111</v>
       </c>
       <c r="G21" t="n">
         <v>0.1124</v>
@@ -2092,13 +2092,13 @@
         <v>0.3907</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0545</v>
+        <v>0.3384</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1678</v>
+        <v>0.0344</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2223</v>
+        <v>0.304</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4959</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3791</v>
+        <v>-1.0083</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9141</v>
+        <v>1.0152</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2932</v>
+        <v>-2.0236</v>
       </c>
       <c r="G22" t="n">
         <v>1.2521</v>
@@ -2170,13 +2170,13 @@
         <v>0.3907</v>
       </c>
       <c r="S22" t="n">
-        <v>0.033</v>
+        <v>0.4037</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2943</v>
+        <v>-0.1931</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3272</v>
+        <v>0.5969</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8828</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8394</v>
+        <v>-1.9834</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7201</v>
+        <v>-3.0235</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8807</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
         <v>-1.5348</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1446</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2805</v>
+        <v>-0.5838</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4251</v>
+        <v>0.5845</v>
       </c>
       <c r="V23" t="n">
         <v>0.3321</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.2376</v>
+        <v>-4.0821</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0987</v>
+        <v>-3.9976</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1389</v>
+        <v>-0.0844</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7483</v>
@@ -2326,13 +2326,13 @@
         <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4408</v>
+        <v>0.5964</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0689</v>
+        <v>0.17</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3719</v>
+        <v>0.4264</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.849</v>
+        <v>-4.4224</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8379</v>
+        <v>-2.7368</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.0111</v>
+        <v>-1.6856</v>
       </c>
       <c r="G25" t="n">
         <v>-0.5973000000000001</v>
@@ -2404,13 +2404,13 @@
         <v>0.3907</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.8964</v>
+        <v>-0.4698</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5447</v>
+        <v>-0.4436</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.3517</v>
+        <v>-0.0262</v>
       </c>
       <c r="V25" t="n">
         <v>-2.7693</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>6.391400000000001</v>
+        <v>8.413799999999998</v>
       </c>
       <c r="E26" t="n">
-        <v>13.0926</v>
+        <v>13.0924</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.701199999999999</v>
+        <v>-4.678800000000001</v>
       </c>
       <c r="G26" t="n">
         <v>3.3673</v>
@@ -2482,16 +2482,16 @@
         <v>7.8139</v>
       </c>
       <c r="S26" t="n">
-        <v>0.09599999999999975</v>
+        <v>2.1182</v>
       </c>
       <c r="T26" t="n">
         <v>-2.4062</v>
       </c>
       <c r="U26" t="n">
-        <v>2.5022</v>
+        <v>4.5247</v>
       </c>
       <c r="V26" t="n">
-        <v>7.811400000000003</v>
+        <v>7.811400000000001</v>
       </c>
       <c r="W26" t="n">
         <v>15.7902</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484233_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484233_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,28 +570,28 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.8879</v>
+        <v>8.273899999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9667</v>
+        <v>6.3527</v>
       </c>
       <c r="F2" t="n">
         <v>1.9212</v>
       </c>
       <c r="G2" t="n">
-        <v>5.333</v>
+        <v>4.719</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.7235</v>
+        <v>-1.3374</v>
       </c>
       <c r="I2" t="n">
         <v>6.0564</v>
       </c>
       <c r="J2" t="n">
-        <v>6.7204</v>
+        <v>6.1064</v>
       </c>
       <c r="K2" t="n">
-        <v>1.068</v>
+        <v>0.4541</v>
       </c>
       <c r="L2" t="n">
         <v>5.6524</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0.3979</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2077</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-2.9808</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9529</v>
+        <v>1.5279</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.5316</v>
+        <v>1.5279</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4845</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0424</v>
+        <v>1.5279</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.0921</v>
+        <v>0.921</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0497</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5621</v>
+        <v>1.5279</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.9379</v>
+        <v>0.921</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5197000000000001</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1542</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7999000000000001</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3392</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4607</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3711</v>
+        <v>0.9529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3558</v>
+        <v>-1.5316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0153</v>
+        <v>2.4845</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4441</v>
+        <v>-0.0424</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4032</v>
+        <v>-2.0921</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0409</v>
+        <v>2.0497</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2774</v>
+        <v>-0.5621</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3712</v>
+        <v>-1.9379</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.09379999999999999</v>
+        <v>1.3758</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8334</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.968</v>
+        <v>-0.1542</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1346</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8542999999999999</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7262999999999999</v>
+        <v>0.3392</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.128</v>
+        <v>0.4607</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8253</v>
+        <v>0.614</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1573</v>
+        <v>0.614</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0717</v>
+        <v>0.614</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2384</v>
+        <v>0.614</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3101</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0814</v>
+        <v>0.614</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0409</v>
+        <v>0.614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0097</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2793</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.229</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.262</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.033</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1068,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9631999999999999</v>
+        <v>0.3711</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1202</v>
+        <v>0.3558</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8431</v>
+        <v>0.0153</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.7528</v>
+        <v>0.4441</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.07829999999999999</v>
+        <v>0.4032</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6745</v>
+        <v>0.0409</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0614</v>
+        <v>1.2774</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0614</v>
+        <v>1.3712</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8142</v>
+        <v>-0.8334</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1397</v>
+        <v>-0.968</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6745</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1953</v>
+        <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4058</v>
+        <v>-0.8542999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1816</v>
+        <v>-0.7262999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2242</v>
+        <v>-0.128</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1094,12 +1129,17 @@
       </c>
       <c r="X8" t="n">
         <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OBIOLS PUIG</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1991</v>
+        <v>-0.8253</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5696</v>
+        <v>-1.1573</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.7687</v>
+        <v>0.3321</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5013</v>
+        <v>0.0717</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0049</v>
+        <v>-0.2384</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4964</v>
+        <v>0.3101</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0716</v>
+        <v>0.0814</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7585</v>
+        <v>0.0409</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6869</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5729</v>
+        <v>-0.0097</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7634</v>
+        <v>-0.2793</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8095</v>
+        <v>0.2696</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4436</v>
+        <v>-0.229</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3885</v>
+        <v>-0.262</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0551</v>
+        <v>0.033</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.817</v>
+        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7035</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.1578</v>
+        <v>-0.9631999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3306</v>
+        <v>-0.1202</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.8272</v>
+        <v>-0.8431</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6207</v>
+        <v>-0.7528</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0133</v>
+        <v>-0.07829999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.634</v>
+        <v>-0.6745</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3283</v>
+        <v>0.0614</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2878</v>
+        <v>0.0614</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.949</v>
+        <v>-0.8142</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2745</v>
+        <v>-0.1397</v>
       </c>
       <c r="O10" t="n">
         <v>-0.6745</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0.1953</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0722</v>
+        <v>-0.4058</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0406</v>
+        <v>-0.1816</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0316</v>
+        <v>-0.2242</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1052</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>M. OBIOLS PUIG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2925</v>
+        <v>-2.1991</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3151</v>
+        <v>0.5696</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9774</v>
+        <v>-2.7687</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.3877</v>
+        <v>-1.5013</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7427</v>
+        <v>-0.0049</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.6451</v>
+        <v>-1.4964</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0244</v>
+        <v>0.0716</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3236</v>
+        <v>0.7585</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.7007</v>
+        <v>-0.6869</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3634</v>
+        <v>-1.5729</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.419</v>
+        <v>-0.7634</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9443</v>
+        <v>-0.8095</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4423</v>
+        <v>-0.4436</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7093</v>
+        <v>-0.3885</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2669</v>
+        <v>-0.0551</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.7145</v>
+        <v>-1.817</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7145</v>
+        <v>-2.7035</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. VIEJO ANDREU</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8912</v>
+        <v>-3.1578</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7422</v>
+        <v>-0.3306</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.149</v>
+        <v>-2.8272</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.5112</v>
+        <v>-0.6207</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8683</v>
+        <v>0.0133</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.6429</v>
+        <v>-0.634</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9245</v>
+        <v>0.3283</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6306</v>
+        <v>0.2878</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2939</v>
+        <v>0.0405</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5866</v>
+        <v>-0.949</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2377</v>
+        <v>-0.2745</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.349</v>
+        <v>-0.6745</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4795</v>
+        <v>0.0722</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1906</v>
+        <v>0.0406</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2888</v>
+        <v>0.0316</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2735</v>
+        <v>-1.8279</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1638</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.4373</v>
+        <v>-2.1052</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3817</v>
+        <v>-4.8204</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.4387</v>
+        <v>-1.8431</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.943</v>
+        <v>-2.9774</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.9085</v>
+        <v>-3.9157</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.1507</v>
+        <v>-1.6636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2422</v>
+        <v>-2.2521</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.1863</v>
+        <v>-2.5523</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.4291</v>
+        <v>-1.2446</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2428</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.7223</v>
+        <v>-1.3634</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.7217</v>
+        <v>-0.419</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.9443</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>1.3674</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0701</v>
+        <v>0.4423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5762</v>
+        <v>0.7093</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5061</v>
+        <v>-0.2669</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.817</v>
+        <v>-2.7145</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.0942</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. VIEJO ANDREU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,229 +1566,240 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.786100000000002</v>
+        <v>-5.8912</v>
       </c>
       <c r="E14" t="n">
-        <v>7.306400000000001</v>
+        <v>-1.7422</v>
       </c>
       <c r="F14" t="n">
-        <v>-13.0925</v>
+        <v>-4.149</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.367400000000001</v>
+        <v>-4.5112</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.0892</v>
+        <v>-1.8683</v>
       </c>
       <c r="I14" t="n">
-        <v>4.721699999999998</v>
+        <v>-2.6429</v>
       </c>
       <c r="J14" t="n">
-        <v>9.0382</v>
+        <v>-1.9245</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2893</v>
+        <v>-0.6306</v>
       </c>
       <c r="L14" t="n">
-        <v>6.749099999999999</v>
+        <v>-1.2939</v>
       </c>
       <c r="M14" t="n">
-        <v>-12.4058</v>
+        <v>-2.5866</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.3786</v>
+        <v>-1.2377</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0273</v>
+        <v>-1.349</v>
       </c>
       <c r="P14" t="n">
-        <v>4.883599999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="Q14" t="n">
-        <v>-7.813599999999999</v>
+        <v>-1.1721</v>
       </c>
       <c r="R14" t="n">
-        <v>12.6971</v>
+        <v>0.586</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5093000000000001</v>
+        <v>0.4795</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.8971</v>
+        <v>0.1906</v>
       </c>
       <c r="U14" t="n">
-        <v>2.4064</v>
+        <v>0.2888</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.811400000000001</v>
+        <v>-1.2735</v>
       </c>
       <c r="W14" t="n">
-        <v>7.978899999999999</v>
+        <v>1.1638</v>
       </c>
       <c r="X14" t="n">
-        <v>-15.7904</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0594</v>
+        <v>-6.3817</v>
       </c>
       <c r="E15" t="n">
-        <v>6.3586</v>
+        <v>-4.4387</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7007</v>
+        <v>-1.943</v>
       </c>
       <c r="G15" t="n">
-        <v>4.4891</v>
+        <v>-3.9085</v>
       </c>
       <c r="H15" t="n">
-        <v>5.9868</v>
+        <v>-4.1507</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.4976</v>
+        <v>0.2422</v>
       </c>
       <c r="J15" t="n">
-        <v>6.082</v>
+        <v>-2.1863</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9606</v>
+        <v>-2.4291</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1214</v>
+        <v>0.2428</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5929</v>
+        <v>-1.7223</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0261</v>
+        <v>-1.7217</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.619</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1721</v>
+        <v>1.3674</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9842</v>
+        <v>-0.0701</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4146</v>
+        <v>-0.5762</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3988</v>
+        <v>0.5061</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6093</v>
+        <v>-1.817</v>
       </c>
       <c r="W15" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-2.0942</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.95</v>
+        <v>-5.786099999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>9.133599999999999</v>
+        <v>7.306299999999996</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1836</v>
+        <v>-13.0925</v>
       </c>
       <c r="G16" t="n">
-        <v>4.465</v>
+        <v>-3.3675</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0133</v>
+        <v>-8.088999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4783</v>
+        <v>4.721700000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>6.5324</v>
+        <v>9.0382</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4349</v>
+        <v>2.289399999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>6.0975</v>
+        <v>6.749099999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.0674</v>
+        <v>-12.4058</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4482</v>
+        <v>-10.3786</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.6192</v>
+        <v>-2.0273</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9534</v>
+        <v>4.883599999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.1255</v>
+        <v>-7.813599999999999</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1721</v>
+        <v>12.6971</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4361</v>
+        <v>0.5093000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6435999999999999</v>
+        <v>-1.8971</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2075</v>
+        <v>2.406400000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>4.8745</v>
+        <v>-7.811400000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>6.3704</v>
+        <v>7.978899999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.4959</v>
-      </c>
+        <v>-15.7904</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.8372</v>
+        <v>7.0594</v>
       </c>
       <c r="E17" t="n">
-        <v>5.0646</v>
+        <v>6.3586</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7726</v>
+        <v>0.7007</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1255</v>
+        <v>4.4891</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5621</v>
+        <v>5.9868</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6875</v>
+        <v>-1.4976</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1753</v>
+        <v>6.082</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5116000000000001</v>
+        <v>5.9606</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6869</v>
+        <v>0.1214</v>
       </c>
       <c r="M17" t="n">
-        <v>0.0498</v>
+        <v>-1.5929</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0504</v>
+        <v>0.0261</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-1.619</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0378</v>
+        <v>0.9842</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1808</v>
+        <v>-0.4146</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2186</v>
+        <v>1.3988</v>
       </c>
       <c r="V17" t="n">
-        <v>6.3155</v>
+        <v>0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>6.5928</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VERA CUSCOLL</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.983</v>
+        <v>6.95</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3475</v>
+        <v>9.133599999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3645</v>
+        <v>-2.1836</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5328000000000001</v>
+        <v>4.465</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.3034</v>
+        <v>-0.0133</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2294</v>
+        <v>4.4783</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0814</v>
+        <v>6.5324</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0409</v>
+        <v>0.4349</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>6.0975</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6142</v>
+        <v>-2.0674</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3443</v>
+        <v>-0.4482</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2698</v>
+        <v>-1.6192</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-3.1255</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>0.379</v>
+        <v>-0.4361</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2428</v>
+        <v>-0.6435999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1362</v>
+        <v>0.2075</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9414</v>
+        <v>4.8745</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>6.3704</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>A. BARQUETS ARIZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3836</v>
+        <v>5.8372</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0078</v>
+        <v>5.0646</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3914</v>
+        <v>0.7726</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2611</v>
+        <v>-0.1255</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.089</v>
+        <v>0.5621</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3502</v>
+        <v>-0.6875</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4109</v>
+        <v>-0.1753</v>
       </c>
       <c r="K19" t="n">
-        <v>0.33</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>-0.6869</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1498</v>
+        <v>0.0498</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.419</v>
+        <v>0.0504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2692</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3907</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3411</v>
+        <v>0.0378</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1087</v>
+        <v>-0.1808</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2324</v>
+        <v>0.2186</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6093</v>
+        <v>6.3155</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>6.5928</v>
       </c>
       <c r="X19" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>E. VERA CUSCOLL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4535</v>
+        <v>0.983</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0228</v>
+        <v>1.3475</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4307</v>
+        <v>-0.3645</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6737</v>
+        <v>-0.5328000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7043</v>
+        <v>-0.3034</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9694</v>
+        <v>-0.2294</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8207</v>
+        <v>0.0814</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8749</v>
+        <v>0.0409</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0543</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.853</v>
+        <v>-0.6142</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1707</v>
+        <v>-0.3443</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0237</v>
+        <v>-0.2698</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0571</v>
+        <v>0.379</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5026</v>
+        <v>0.2428</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4456</v>
+        <v>0.1362</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4959</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4959</v>
+        <v>1.2186</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8497</v>
+        <v>0.3836</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0386</v>
+        <v>-0.0078</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8111</v>
+        <v>0.3914</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1124</v>
+        <v>0.2611</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0722</v>
+        <v>-0.089</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0403</v>
+        <v>0.3502</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1223</v>
+        <v>0.4109</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0819</v>
+        <v>0.33</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0405</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.009900000000000001</v>
+        <v>-0.1498</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0097</v>
+        <v>-0.419</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0002</v>
+        <v>0.2692</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.1953</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3384</v>
+        <v>0.3411</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0344</v>
+        <v>0.1087</v>
       </c>
       <c r="U21" t="n">
-        <v>0.304</v>
+        <v>0.2324</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>-0.6093</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0083</v>
+        <v>-0.4535</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0152</v>
+        <v>-0.0228</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0236</v>
+        <v>-0.4307</v>
       </c>
       <c r="G22" t="n">
-        <v>1.2521</v>
+        <v>-2.6737</v>
       </c>
       <c r="H22" t="n">
-        <v>1.9404</v>
+        <v>-0.7043</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6883</v>
+        <v>-1.9694</v>
       </c>
       <c r="J22" t="n">
-        <v>2.4353</v>
+        <v>-0.8207</v>
       </c>
       <c r="K22" t="n">
-        <v>2.988</v>
+        <v>-0.8749</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5527</v>
+        <v>0.0543</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1832</v>
+        <v>-1.853</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0476</v>
+        <v>0.1707</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1356</v>
+        <v>-2.0237</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>0.7814</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4037</v>
+        <v>-0.0571</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1931</v>
+        <v>-0.5026</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5969</v>
+        <v>0.4456</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8828</v>
+        <v>1.4959</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.0549</v>
+        <v>1.4959</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9834</v>
+        <v>-0.8497</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.0235</v>
+        <v>-0.0386</v>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>-0.8111</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5348</v>
+        <v>0.1124</v>
       </c>
       <c r="H23" t="n">
-        <v>1.0412</v>
+        <v>0.0722</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.576</v>
+        <v>0.0403</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4862</v>
+        <v>0.1223</v>
       </c>
       <c r="K23" t="n">
-        <v>1.4147</v>
+        <v>0.0819</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9009</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0485</v>
+        <v>-0.009900000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3735</v>
+        <v>-0.0097</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6751</v>
+        <v>-0.0002</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0005999999999999999</v>
+        <v>0.3384</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5838</v>
+        <v>0.0344</v>
       </c>
       <c r="U23" t="n">
-        <v>0.5845</v>
+        <v>0.304</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3321</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0821</v>
+        <v>-1.0083</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9976</v>
+        <v>1.0152</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0844</v>
+        <v>-2.0236</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.7483</v>
+        <v>1.2521</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2893</v>
+        <v>1.9404</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4589</v>
+        <v>-0.6883</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.124</v>
+        <v>2.4353</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.2049</v>
+        <v>2.988</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0809</v>
+        <v>-0.5527</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.6243</v>
+        <v>-1.1832</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.0844</v>
+        <v>-1.0476</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5399</v>
+        <v>-0.1356</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9301</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.3208</v>
+        <v>-1.1721</v>
       </c>
       <c r="R24" t="n">
         <v>0.3907</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5964</v>
+        <v>0.4037</v>
       </c>
       <c r="T24" t="n">
-        <v>0.17</v>
+        <v>-0.1931</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4264</v>
+        <v>0.5969</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.8828</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.2772</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q. ROIG GARCIA</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.4224</v>
+        <v>-1.9834</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7368</v>
+        <v>-3.0235</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.6856</v>
+        <v>1.04</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.5973000000000001</v>
+        <v>-1.5348</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8859</v>
+        <v>1.0412</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.4832</v>
+        <v>-2.576</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6524</v>
+        <v>-0.4862</v>
       </c>
       <c r="K25" t="n">
-        <v>0.6958</v>
+        <v>1.4147</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3482</v>
+        <v>-1.9009</v>
       </c>
       <c r="M25" t="n">
-        <v>0.0551</v>
+        <v>-1.0485</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1901</v>
+        <v>-0.3735</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.135</v>
+        <v>-0.6751</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4698</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4436</v>
+        <v>-0.5838</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0262</v>
+        <v>0.5845</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.7693</v>
+        <v>0.3321</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.1052</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-4.0821</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.9976</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.7483</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.2893</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4589</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.124</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.2049</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.0809</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.6243</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.3208</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.5964</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q. ROIG GARCIA</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-4.4224</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-2.7368</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-1.6856</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-0.5973000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8859</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-1.4832</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.6524</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.6958</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.135</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.4698</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.4436</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.0262</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-2.7693</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-2.1052</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484233_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>8.413799999999998</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>13.0924</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F28" t="n">
         <v>-4.678800000000001</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G28" t="n">
         <v>3.3673</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H28" t="n">
         <v>8.0893</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>-4.721500000000001</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J28" t="n">
         <v>12.4057</v>
       </c>
-      <c r="K26" t="n">
+      <c r="K28" t="n">
         <v>10.3786</v>
       </c>
-      <c r="L26" t="n">
+      <c r="L28" t="n">
         <v>2.027300000000001</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M28" t="n">
         <v>-9.038300000000001</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>-2.2894</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>-6.7489</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>-4.8836</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>7.8139</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>2.1182</v>
       </c>
-      <c r="T26" t="n">
+      <c r="T28" t="n">
         <v>-2.4062</v>
       </c>
-      <c r="U26" t="n">
+      <c r="U28" t="n">
         <v>4.5247</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>7.811400000000001</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>15.7902</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-7.9788</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
